--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009BCDB3-116E-4009-A0F0-2914C856EDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2DC987-65F5-4893-B58C-5865206EDD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关键词回答" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t>关键词自动回答表</t>
   </si>
@@ -191,6 +191,14 @@
   </si>
   <si>
     <t>饿就吃饭</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉豪</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡明铮</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -609,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F23"/>
+  <dimension ref="B1:F24"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -823,6 +831,14 @@
       </c>
       <c r="C23" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2DC987-65F5-4893-B58C-5865206EDD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31231899-55EE-4F0A-8D57-1291677F0132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,11 +194,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>嘉豪</t>
+    <t>蔡明铮</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>蔡明铮</t>
+    <t>arch linux高手</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -835,10 +835,10 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
         <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
